--- a/tame_output/ON/bt/strategyON_20240129.xlsx
+++ b/tame_output/ON/bt/strategyON_20240129.xlsx
@@ -600,7 +600,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.8%</t>
+          <t>52.7%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -610,16 +610,16 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.80</t>
+          <t>0.79</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>53.2%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,7 +628,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.1%</t>
+          <t>0.7%</t>
         </is>
       </c>
     </row>
@@ -758,7 +758,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>78.0%</t>
+          <t>77.8%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -768,7 +768,7 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>2.72</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,7 +786,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -849,7 +849,7 @@
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>64.6%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>2.4%</t>
+          <t>2.0%</t>
         </is>
       </c>
     </row>
@@ -916,7 +916,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>31.2%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -926,7 +926,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -935,7 +935,7 @@
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,7 +944,7 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -1007,7 +1007,7 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>53.5%</t>
+          <t>53.1%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
@@ -1032,7 +1032,7 @@
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-20.0%</t>
+          <t>-20.1%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>3.5%</t>
+          <t>2.3%</t>
         </is>
       </c>
     </row>
@@ -1074,7 +1074,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>101.1%</t>
+          <t>100.7%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1084,7 +1084,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3.25</t>
+          <t>3.24</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1093,7 +1093,7 @@
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,7 +1102,7 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>8.4%</t>
+          <t>8.3%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,7 +1165,7 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>96.4%</t>
+          <t>96.0%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>3.8%</t>
+          <t>2.9%</t>
         </is>
       </c>
     </row>
@@ -1232,7 +1232,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.6%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>2.16</t>
+          <t>2.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>66.9%</t>
+          <t>66.5%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
@@ -1348,7 +1348,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.7%</t>
+          <t>-155.8%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>2.5%</t>
+          <t>1.3%</t>
         </is>
       </c>
     </row>
@@ -1390,7 +1390,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>130.3%</t>
+          <t>129.7%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1400,7 +1400,7 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>4.10</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1409,7 +1409,7 @@
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,7 +1418,7 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-01-27</t>
+          <t>2024-01-28</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.1%</t>
+          <t>9.0%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
@@ -1481,7 +1481,7 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>124.1%</t>
+          <t>123.5%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>3.9%</t>
+          <t>2.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1856"/>
+  <dimension ref="A1:G1857"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44233,7 +44233,7 @@
         <v>45318</v>
       </c>
       <c r="B1856" t="n">
-        <v>3.291648619981434</v>
+        <v>3.299136146347057</v>
       </c>
       <c r="C1856" t="n">
         <v>3.139859661206862</v>
@@ -44249,6 +44249,29 @@
       </c>
       <c r="G1856" t="n">
         <v>4.49874440381718</v>
+      </c>
+    </row>
+    <row r="1857">
+      <c r="A1857" s="2" t="n">
+        <v>45319</v>
+      </c>
+      <c r="B1857" t="n">
+        <v>3.287799389351032</v>
+      </c>
+      <c r="C1857" t="n">
+        <v>3.13596571986312</v>
+      </c>
+      <c r="D1857" t="n">
+        <v>1.639223870765262</v>
+      </c>
+      <c r="E1857" t="n">
+        <v>3.791298843855477</v>
+      </c>
+      <c r="F1857" t="n">
+        <v>2.253303419352245</v>
+      </c>
+      <c r="G1857" t="n">
+        <v>4.487947771474467</v>
       </c>
     </row>
   </sheetData>
